--- a/Mx/SkienAlgsListMx2025.xlsx
+++ b/Mx/SkienAlgsListMx2025.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urfume-my.sharepoint.com/personal/sergey_osipov_urfu_me/Documents/AiSD2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://urfume-my.sharepoint.com/personal/sergey_osipov_urfu_me/Documents/AiSD2026/Mx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1308" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{628E2E06-DD34-4B30-9444-87562280CCF4}"/>
+  <xr:revisionPtr revIDLastSave="1339" documentId="13_ncr:1_{BB64072A-02B6-4C3F-B1E2-71C6B558E3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D62B583-8998-43C5-A035-6B15E98E7D87}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="870" windowWidth="17865" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="327">
   <si>
     <t>Листинг</t>
   </si>
@@ -1030,6 +1030,18 @@
   </si>
   <si>
     <t>Иванов Вячеслав Александрович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старицын Михаил Вячеславович </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Звягинцев Роман Евгеньевич </t>
+  </si>
+  <si>
+    <t>Резанов Аристарх Сергеевич</t>
+  </si>
+  <si>
+    <t>Токарев Николай Евгеньевич</t>
   </si>
 </sst>
 </file>
@@ -1135,13 +1147,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -1159,6 +1164,13 @@
       <color rgb="FF000000"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1208,16 +1220,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1242,6 +1251,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1705,12 +1715,12 @@
       <c r="E2" s="3">
         <v>11</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G2" s="13"/>
+      <c r="G2" s="12"/>
       <c r="H2" s="3" t="str" cm="1">
-        <f t="array" ref="H2:H9">_xlfn.UNIQUE($F$2:$F$107)</f>
+        <f t="array" ref="H2:H13">_xlfn.UNIQUE($F$2:$F$107)</f>
         <v>Косоногова Анна Михайловна</v>
       </c>
       <c r="I2" s="4">
@@ -1734,16 +1744,16 @@
       <c r="E3" s="3">
         <v>13</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G3" s="13"/>
+      <c r="G3" s="12"/>
       <c r="H3" s="3" t="str">
         <v>Черев Алексей Дмитриевич</v>
       </c>
       <c r="I3" s="4">
         <f>SUMIF(F3:F108, H3, E3:E108)</f>
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1762,23 +1772,23 @@
       <c r="E4" s="3">
         <v>16</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G4" s="13"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="3" t="str">
-        <v xml:space="preserve">Бахтеева Вероника Александровна </v>
+        <v>Токарев Николай Евгеньевич</v>
       </c>
       <c r="I4" s="4">
         <f>SUMIF(F4:F108, H4, E4:E108)</f>
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="22"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
@@ -1788,7 +1798,7 @@
       <c r="E5" s="3">
         <v>8</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="23" t="s">
         <v>316</v>
       </c>
       <c r="G5" s="8"/>
@@ -1816,10 +1826,10 @@
       <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G6" s="13"/>
+      <c r="G6" s="12"/>
       <c r="H6" s="3" t="str">
         <v>Цюкало Кирилл Алексеевич</v>
       </c>
@@ -1844,10 +1854,10 @@
       <c r="E7" s="3">
         <v>4</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G7" s="13"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="3" t="str">
         <v xml:space="preserve">Пасюта Мария Сергеевна </v>
       </c>
@@ -1872,16 +1882,16 @@
       <c r="E8" s="3">
         <v>10</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="23" t="s">
         <v>316</v>
       </c>
-      <c r="G8" s="16"/>
+      <c r="G8" s="15"/>
       <c r="H8" s="3" t="str">
-        <v>Милицина Елизавета Сергеевна</v>
+        <v xml:space="preserve">Бахтеева Вероника Александровна </v>
       </c>
       <c r="I8" s="4">
         <f t="shared" si="0"/>
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1900,16 +1910,16 @@
       <c r="E9" s="3">
         <v>7</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G9" s="16"/>
+      <c r="G9" s="15"/>
       <c r="H9" s="5" t="str">
-        <v>Иванов Вячеслав Александрович</v>
+        <v>Милицина Елизавета Сергеевна</v>
       </c>
       <c r="I9" s="4">
         <f t="shared" si="0"/>
-        <v>205</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1928,14 +1938,16 @@
       <c r="E10" s="3">
         <v>10</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="3"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="3" t="str">
+        <v xml:space="preserve">Старицын Михаил Вячеславович </v>
+      </c>
       <c r="I10" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1954,17 +1966,19 @@
       <c r="E11" s="3">
         <v>12</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="4"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="4" t="str">
+        <v>Резанов Аристарх Сергеевич</v>
+      </c>
       <c r="I11" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
@@ -1981,16 +1995,18 @@
         <v>6</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="3"/>
+        <v>326</v>
+      </c>
+      <c r="G12" s="12"/>
+      <c r="H12" s="3" t="str">
+        <v xml:space="preserve">Звягинцев Роман Евгеньевич </v>
+      </c>
       <c r="I12" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
@@ -2007,16 +2023,18 @@
         <v>13</v>
       </c>
       <c r="F13" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="3"/>
+        <v>326</v>
+      </c>
+      <c r="G13" s="12"/>
+      <c r="H13" s="3" t="str">
+        <v>Иванов Вячеслав Александрович</v>
+      </c>
       <c r="I13" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>42</v>
       </c>
@@ -2033,16 +2051,16 @@
         <v>10</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" s="17"/>
+        <v>326</v>
+      </c>
+      <c r="G14" s="16"/>
       <c r="H14" s="6"/>
       <c r="I14" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>45</v>
       </c>
@@ -2059,16 +2077,16 @@
         <v>8</v>
       </c>
       <c r="F15" s="24" t="s">
-        <v>317</v>
-      </c>
-      <c r="G15" s="18"/>
+        <v>326</v>
+      </c>
+      <c r="G15" s="17"/>
       <c r="H15" s="3"/>
       <c r="I15" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>48</v>
       </c>
@@ -2085,9 +2103,9 @@
         <v>16</v>
       </c>
       <c r="F16" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="G16" s="13"/>
+        <v>326</v>
+      </c>
+      <c r="G16" s="12"/>
       <c r="H16" s="3"/>
       <c r="I16" s="4">
         <f t="shared" si="0"/>
@@ -2111,7 +2129,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="8"/>
-      <c r="G17" s="18"/>
+      <c r="G17" s="17"/>
       <c r="H17" s="3"/>
       <c r="I17" s="4">
         <f t="shared" si="0"/>
@@ -2135,7 +2153,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="4"/>
-      <c r="G18" s="18"/>
+      <c r="G18" s="17"/>
       <c r="H18" s="3"/>
       <c r="I18" s="4">
         <f t="shared" si="0"/>
@@ -2159,7 +2177,7 @@
         <v>4</v>
       </c>
       <c r="F19" s="11"/>
-      <c r="G19" s="19"/>
+      <c r="G19" s="18"/>
       <c r="H19" s="3"/>
       <c r="I19" s="4">
         <f t="shared" si="0"/>
@@ -2182,10 +2200,10 @@
       <c r="E20" s="3">
         <v>9</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="G20" s="19"/>
+      <c r="G20" s="18"/>
       <c r="H20" s="3"/>
       <c r="I20" s="4">
         <f t="shared" si="0"/>
@@ -2208,10 +2226,10 @@
       <c r="E21" s="3">
         <v>18</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="F21" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="G21" s="19"/>
+      <c r="G21" s="18"/>
       <c r="H21" s="3"/>
       <c r="I21" s="4">
         <f t="shared" si="0"/>
@@ -2234,10 +2252,10 @@
       <c r="E22" s="3">
         <v>10</v>
       </c>
-      <c r="F22" s="24" t="s">
+      <c r="F22" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="G22" s="19"/>
+      <c r="G22" s="18"/>
       <c r="H22" s="8"/>
       <c r="I22" s="4">
         <f t="shared" si="0"/>
@@ -2260,10 +2278,10 @@
       <c r="E23" s="3">
         <v>30</v>
       </c>
-      <c r="F23" s="24" t="s">
+      <c r="F23" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="G23" s="19"/>
+      <c r="G23" s="18"/>
       <c r="H23" s="3"/>
       <c r="I23" s="4">
         <f t="shared" si="0"/>
@@ -2286,10 +2304,10 @@
       <c r="E24" s="3">
         <v>8</v>
       </c>
-      <c r="F24" s="24" t="s">
+      <c r="F24" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G24" s="19"/>
+      <c r="G24" s="18"/>
       <c r="H24" s="3"/>
       <c r="I24" s="4">
         <f t="shared" si="0"/>
@@ -2312,10 +2330,10 @@
       <c r="E25" s="3">
         <v>10</v>
       </c>
-      <c r="F25" s="24" t="s">
+      <c r="F25" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G25" s="19"/>
+      <c r="G25" s="18"/>
       <c r="H25" s="3"/>
       <c r="I25" s="4">
         <f t="shared" si="0"/>
@@ -2338,10 +2356,10 @@
       <c r="E26" s="3">
         <v>10</v>
       </c>
-      <c r="F26" s="24" t="s">
+      <c r="F26" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G26" s="19"/>
+      <c r="G26" s="18"/>
       <c r="H26" s="3"/>
       <c r="I26" s="4">
         <f t="shared" si="0"/>
@@ -2364,10 +2382,10 @@
       <c r="E27" s="3">
         <v>7</v>
       </c>
-      <c r="F27" s="24" t="s">
+      <c r="F27" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G27" s="20"/>
+      <c r="G27" s="19"/>
       <c r="H27" s="3"/>
       <c r="I27" s="4">
         <f t="shared" si="0"/>
@@ -2390,10 +2408,10 @@
       <c r="E28" s="3">
         <v>9</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="G28" s="20"/>
+      <c r="G28" s="19"/>
       <c r="H28" s="3"/>
       <c r="I28" s="4">
         <f t="shared" si="0"/>
@@ -2416,10 +2434,10 @@
       <c r="E29" s="3">
         <v>22</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G29" s="17"/>
+      <c r="G29" s="16"/>
       <c r="H29" s="3"/>
       <c r="I29" s="4">
         <f t="shared" si="0"/>
@@ -2442,10 +2460,10 @@
       <c r="E30" s="3">
         <v>8</v>
       </c>
-      <c r="F30" s="24" t="s">
+      <c r="F30" s="23" t="s">
         <v>320</v>
       </c>
-      <c r="G30" s="13"/>
+      <c r="G30" s="12"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4">
         <f t="shared" si="0"/>
@@ -2468,8 +2486,10 @@
       <c r="E31" s="3">
         <v>15</v>
       </c>
-      <c r="F31" s="11"/>
-      <c r="G31" s="13"/>
+      <c r="F31" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="G31" s="12"/>
       <c r="H31" s="3"/>
       <c r="I31" s="4">
         <f t="shared" si="0"/>
@@ -2492,10 +2512,10 @@
       <c r="E32" s="3">
         <v>15</v>
       </c>
-      <c r="F32" s="24" t="s">
-        <v>318</v>
-      </c>
-      <c r="G32" s="13"/>
+      <c r="F32" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="G32" s="12"/>
       <c r="H32" s="4"/>
       <c r="I32" s="4">
         <f t="shared" si="0"/>
@@ -2518,8 +2538,10 @@
       <c r="E33" s="3">
         <v>13</v>
       </c>
-      <c r="F33" s="11"/>
-      <c r="G33" s="13"/>
+      <c r="F33" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="G33" s="12"/>
       <c r="H33" s="3"/>
       <c r="I33" s="4">
         <f t="shared" si="0"/>
@@ -2542,10 +2564,10 @@
       <c r="E34" s="3">
         <v>12</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G34" s="13"/>
+      <c r="G34" s="12"/>
       <c r="H34" s="3"/>
       <c r="I34" s="4">
         <f t="shared" si="0"/>
@@ -2568,10 +2590,10 @@
       <c r="E35" s="3">
         <v>11</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G35" s="18"/>
+      <c r="G35" s="17"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4">
         <f t="shared" si="0"/>
@@ -2594,10 +2616,10 @@
       <c r="E36" s="3">
         <v>14</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G36" s="13"/>
+      <c r="G36" s="12"/>
       <c r="H36" s="4"/>
       <c r="I36" s="4">
         <f t="shared" si="0"/>
@@ -2620,10 +2642,10 @@
       <c r="E37" s="3">
         <v>13</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G37" s="13"/>
+      <c r="G37" s="12"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4">
         <f t="shared" si="0"/>
@@ -2646,10 +2668,10 @@
       <c r="E38" s="3">
         <v>9</v>
       </c>
-      <c r="F38" s="24" t="s">
+      <c r="F38" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G38" s="13"/>
+      <c r="G38" s="12"/>
       <c r="H38" s="3"/>
       <c r="I38" s="4">
         <f t="shared" si="0"/>
@@ -2672,10 +2694,10 @@
       <c r="E39" s="3">
         <v>28</v>
       </c>
-      <c r="F39" s="24" t="s">
+      <c r="F39" s="23" t="s">
         <v>318</v>
       </c>
-      <c r="G39" s="13"/>
+      <c r="G39" s="12"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4">
         <f t="shared" si="0"/>
@@ -2698,10 +2720,10 @@
       <c r="E40" s="3">
         <v>3</v>
       </c>
-      <c r="F40" s="24" t="s">
+      <c r="F40" s="23" t="s">
         <v>321</v>
       </c>
-      <c r="G40" s="21"/>
+      <c r="G40" s="20"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4">
         <f t="shared" si="0"/>
@@ -2724,8 +2746,10 @@
       <c r="E41" s="3">
         <v>3</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="21"/>
+      <c r="F41" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G41" s="20"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4">
         <f t="shared" si="0"/>
@@ -2748,8 +2772,10 @@
       <c r="E42" s="3">
         <v>3</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="21"/>
+      <c r="F42" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G42" s="20"/>
       <c r="H42" s="3"/>
       <c r="I42" s="4">
         <f t="shared" si="0"/>
@@ -2772,34 +2798,38 @@
       <c r="E43" s="3">
         <v>3</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="21"/>
+      <c r="F43" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G43" s="20"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4">
-        <f t="shared" si="0"/>
+        <f>SUMIF(F44:F146, H43, E43:E146)</f>
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="22" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="22" t="s">
         <v>129</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="22">
         <v>256</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="22">
         <v>8</v>
       </c>
-      <c r="F44" s="11"/>
-      <c r="G44" s="13"/>
+      <c r="F44" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G44" s="12"/>
       <c r="I44" s="4">
-        <f t="shared" si="0"/>
+        <f>SUMIF(F44:F147, H44, E44:E147)</f>
         <v>0</v>
       </c>
     </row>
@@ -2819,8 +2849,10 @@
       <c r="E45" s="3">
         <v>19</v>
       </c>
-      <c r="F45" s="12"/>
-      <c r="G45" s="19"/>
+      <c r="F45" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G45" s="18"/>
       <c r="I45" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2842,8 +2874,10 @@
       <c r="E46" s="3">
         <v>30</v>
       </c>
-      <c r="F46" s="11"/>
-      <c r="G46" s="21"/>
+      <c r="F46" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="G46" s="20"/>
       <c r="I46" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2866,7 +2900,7 @@
         <v>30</v>
       </c>
       <c r="F47" s="3"/>
-      <c r="G47" s="13"/>
+      <c r="G47" s="12"/>
       <c r="I47" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2889,7 +2923,7 @@
         <v>7</v>
       </c>
       <c r="F48" s="3"/>
-      <c r="G48" s="21"/>
+      <c r="G48" s="20"/>
       <c r="I48" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2912,7 +2946,7 @@
         <v>5</v>
       </c>
       <c r="F49" s="3"/>
-      <c r="G49" s="13"/>
+      <c r="G49" s="12"/>
       <c r="I49" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2935,7 +2969,7 @@
         <v>12</v>
       </c>
       <c r="F50" s="11"/>
-      <c r="G50" s="13"/>
+      <c r="G50" s="12"/>
       <c r="I50" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2958,7 +2992,7 @@
         <v>31</v>
       </c>
       <c r="F51" s="11"/>
-      <c r="G51" s="13"/>
+      <c r="G51" s="12"/>
     </row>
     <row r="52" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
@@ -2976,8 +3010,10 @@
       <c r="E52" s="3">
         <v>16</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="21"/>
+      <c r="F52" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="G52" s="20"/>
     </row>
     <row r="53" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
@@ -2995,8 +3031,10 @@
       <c r="E53" s="3">
         <v>19</v>
       </c>
-      <c r="F53" s="13"/>
-      <c r="G53" s="13"/>
+      <c r="F53" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="G53" s="12"/>
     </row>
     <row r="54" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
@@ -3014,8 +3052,10 @@
       <c r="E54" s="3">
         <v>16</v>
       </c>
-      <c r="F54" s="13"/>
-      <c r="G54" s="13"/>
+      <c r="F54" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="G54" s="12"/>
     </row>
     <row r="55" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
@@ -3033,8 +3073,10 @@
       <c r="E55" s="3">
         <v>30</v>
       </c>
-      <c r="F55" s="11"/>
-      <c r="G55" s="13"/>
+      <c r="F55" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="G55" s="12"/>
     </row>
     <row r="56" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
@@ -3053,7 +3095,7 @@
         <v>12</v>
       </c>
       <c r="F56" s="11"/>
-      <c r="G56" s="13"/>
+      <c r="G56" s="12"/>
     </row>
     <row r="57" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
@@ -3072,7 +3114,7 @@
         <v>41</v>
       </c>
       <c r="F57" s="11"/>
-      <c r="G57" s="13"/>
+      <c r="G57" s="12"/>
     </row>
     <row r="58" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
@@ -3091,7 +3133,7 @@
         <v>17</v>
       </c>
       <c r="F58" s="3"/>
-      <c r="G58" s="21"/>
+      <c r="G58" s="20"/>
     </row>
     <row r="59" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
@@ -3110,7 +3152,7 @@
         <v>5</v>
       </c>
       <c r="F59" s="3"/>
-      <c r="G59" s="21"/>
+      <c r="G59" s="20"/>
     </row>
     <row r="60" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
@@ -3129,7 +3171,7 @@
         <v>32</v>
       </c>
       <c r="F60" s="11"/>
-      <c r="G60" s="13"/>
+      <c r="G60" s="12"/>
     </row>
     <row r="61" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
@@ -3148,7 +3190,7 @@
         <v>42</v>
       </c>
       <c r="F61" s="11"/>
-      <c r="G61" s="21"/>
+      <c r="G61" s="20"/>
     </row>
     <row r="62" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
@@ -3167,7 +3209,7 @@
         <v>4</v>
       </c>
       <c r="F62" s="9"/>
-      <c r="G62" s="21"/>
+      <c r="G62" s="20"/>
     </row>
     <row r="63" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
@@ -3186,7 +3228,7 @@
         <v>15</v>
       </c>
       <c r="F63" s="9"/>
-      <c r="G63" s="18"/>
+      <c r="G63" s="17"/>
     </row>
     <row r="64" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
@@ -3205,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="F64" s="9"/>
-      <c r="G64" s="21"/>
+      <c r="G64" s="20"/>
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
@@ -3224,7 +3266,7 @@
         <v>13</v>
       </c>
       <c r="F65" s="9"/>
-      <c r="G65" s="13"/>
+      <c r="G65" s="12"/>
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
@@ -3243,7 +3285,7 @@
         <v>3</v>
       </c>
       <c r="F66" s="5"/>
-      <c r="G66" s="21"/>
+      <c r="G66" s="20"/>
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
@@ -3262,7 +3304,7 @@
         <v>12</v>
       </c>
       <c r="F67" s="5"/>
-      <c r="G67" s="21"/>
+      <c r="G67" s="20"/>
     </row>
     <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
@@ -3281,7 +3323,7 @@
         <v>12</v>
       </c>
       <c r="F68" s="8"/>
-      <c r="G68" s="21"/>
+      <c r="G68" s="20"/>
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
@@ -3299,8 +3341,10 @@
       <c r="E69" s="3">
         <v>20</v>
       </c>
-      <c r="F69" s="3"/>
-      <c r="G69" s="21"/>
+      <c r="F69" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G69" s="20"/>
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
@@ -3318,8 +3362,8 @@
       <c r="E70" s="3">
         <v>18</v>
       </c>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="12"/>
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
@@ -3337,8 +3381,8 @@
       <c r="E71" s="3">
         <v>5</v>
       </c>
-      <c r="F71" s="14"/>
-      <c r="G71" s="21"/>
+      <c r="F71" s="13"/>
+      <c r="G71" s="20"/>
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
@@ -3357,7 +3401,7 @@
         <v>17</v>
       </c>
       <c r="F72" s="4"/>
-      <c r="G72" s="21"/>
+      <c r="G72" s="20"/>
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
@@ -3375,8 +3419,8 @@
       <c r="E73" s="3">
         <v>14</v>
       </c>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="12"/>
     </row>
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
@@ -3395,7 +3439,7 @@
         <v>5</v>
       </c>
       <c r="F74" s="11"/>
-      <c r="G74" s="13"/>
+      <c r="G74" s="12"/>
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
@@ -3414,7 +3458,7 @@
         <v>28</v>
       </c>
       <c r="F75" s="11"/>
-      <c r="G75" s="13"/>
+      <c r="G75" s="12"/>
     </row>
     <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
@@ -3432,8 +3476,10 @@
       <c r="E76" s="3">
         <v>3</v>
       </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="21"/>
+      <c r="F76" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G76" s="20"/>
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
@@ -3451,8 +3497,10 @@
       <c r="E77" s="3">
         <v>9</v>
       </c>
-      <c r="F77" s="3"/>
-      <c r="G77" s="21"/>
+      <c r="F77" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G77" s="20"/>
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
@@ -3471,7 +3519,7 @@
         <v>13</v>
       </c>
       <c r="F78" s="5"/>
-      <c r="G78" s="13"/>
+      <c r="G78" s="12"/>
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
@@ -3490,7 +3538,7 @@
         <v>15</v>
       </c>
       <c r="F79" s="5"/>
-      <c r="G79" s="13"/>
+      <c r="G79" s="12"/>
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
@@ -3509,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="F80" s="4"/>
-      <c r="G80" s="21"/>
+      <c r="G80" s="20"/>
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
@@ -3528,7 +3576,7 @@
         <v>4</v>
       </c>
       <c r="F81" s="4"/>
-      <c r="G81" s="21"/>
+      <c r="G81" s="20"/>
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
@@ -3546,8 +3594,8 @@
       <c r="E82" s="3">
         <v>5</v>
       </c>
-      <c r="F82" s="15"/>
-      <c r="G82" s="21"/>
+      <c r="F82" s="14"/>
+      <c r="G82" s="20"/>
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
@@ -3566,7 +3614,7 @@
         <v>25</v>
       </c>
       <c r="F83" s="4"/>
-      <c r="G83" s="21"/>
+      <c r="G83" s="20"/>
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
@@ -3585,7 +3633,7 @@
         <v>9</v>
       </c>
       <c r="F84" s="4"/>
-      <c r="G84" s="21"/>
+      <c r="G84" s="20"/>
     </row>
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
@@ -3604,7 +3652,7 @@
         <v>11</v>
       </c>
       <c r="F85" s="4"/>
-      <c r="G85" s="21"/>
+      <c r="G85" s="20"/>
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
@@ -3622,10 +3670,10 @@
       <c r="E86" s="3">
         <v>9</v>
       </c>
-      <c r="F86" s="24" t="s">
+      <c r="F86" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G86" s="13"/>
+      <c r="G86" s="12"/>
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
@@ -3643,10 +3691,10 @@
       <c r="E87" s="3">
         <v>19</v>
       </c>
-      <c r="F87" s="24" t="s">
+      <c r="F87" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G87" s="13"/>
+      <c r="G87" s="12"/>
     </row>
     <row r="88" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
@@ -3664,10 +3712,10 @@
       <c r="E88" s="3">
         <v>10</v>
       </c>
-      <c r="F88" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="G88" s="13"/>
+      <c r="F88" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G88" s="12"/>
     </row>
     <row r="89" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
@@ -3685,10 +3733,10 @@
       <c r="E89" s="3">
         <v>13</v>
       </c>
-      <c r="F89" s="24" t="s">
+      <c r="F89" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G89" s="13"/>
+      <c r="G89" s="12"/>
     </row>
     <row r="90" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
@@ -3706,10 +3754,10 @@
       <c r="E90" s="3">
         <v>16</v>
       </c>
-      <c r="F90" s="24" t="s">
-        <v>322</v>
-      </c>
-      <c r="G90" s="21"/>
+      <c r="F90" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="G90" s="20"/>
     </row>
     <row r="91" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
@@ -3727,10 +3775,10 @@
       <c r="E91" s="3">
         <v>23</v>
       </c>
-      <c r="F91" s="24" t="s">
+      <c r="F91" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G91" s="21"/>
+      <c r="G91" s="20"/>
     </row>
     <row r="92" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
@@ -3748,10 +3796,10 @@
       <c r="E92" s="3">
         <v>5</v>
       </c>
-      <c r="F92" s="24" t="s">
+      <c r="F92" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G92" s="21"/>
+      <c r="G92" s="20"/>
     </row>
     <row r="93" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
@@ -3769,10 +3817,10 @@
       <c r="E93" s="3">
         <v>25</v>
       </c>
-      <c r="F93" s="24" t="s">
+      <c r="F93" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G93" s="21"/>
+      <c r="G93" s="20"/>
     </row>
     <row r="94" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
@@ -3790,10 +3838,10 @@
       <c r="E94" s="3">
         <v>21</v>
       </c>
-      <c r="F94" s="24" t="s">
+      <c r="F94" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G94" s="21"/>
+      <c r="G94" s="20"/>
     </row>
     <row r="95" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
@@ -3811,10 +3859,10 @@
       <c r="E95" s="3">
         <v>16</v>
       </c>
-      <c r="F95" s="24" t="s">
+      <c r="F95" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G95" s="13"/>
+      <c r="G95" s="12"/>
     </row>
     <row r="96" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
@@ -3832,10 +3880,10 @@
       <c r="E96" s="3">
         <v>9</v>
       </c>
-      <c r="F96" s="24" t="s">
+      <c r="F96" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G96" s="21"/>
+      <c r="G96" s="20"/>
     </row>
     <row r="97" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
@@ -3853,10 +3901,10 @@
       <c r="E97" s="3">
         <v>5</v>
       </c>
-      <c r="F97" s="24" t="s">
+      <c r="F97" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G97" s="21"/>
+      <c r="G97" s="20"/>
     </row>
     <row r="98" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
@@ -3874,10 +3922,10 @@
       <c r="E98" s="3">
         <v>14</v>
       </c>
-      <c r="F98" s="24" t="s">
+      <c r="F98" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G98" s="21"/>
+      <c r="G98" s="20"/>
     </row>
     <row r="99" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
@@ -3895,10 +3943,10 @@
       <c r="E99" s="3">
         <v>14</v>
       </c>
-      <c r="F99" s="24" t="s">
+      <c r="F99" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G99" s="21"/>
+      <c r="G99" s="20"/>
     </row>
     <row r="100" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
@@ -3916,10 +3964,10 @@
       <c r="E100" s="3">
         <v>6</v>
       </c>
-      <c r="F100" s="24" t="s">
+      <c r="F100" s="23" t="s">
         <v>322</v>
       </c>
-      <c r="G100" s="13"/>
+      <c r="G100" s="12"/>
     </row>
     <row r="101" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
@@ -3938,7 +3986,7 @@
         <v>22</v>
       </c>
       <c r="F101" s="11"/>
-      <c r="G101" s="13"/>
+      <c r="G101" s="12"/>
     </row>
     <row r="102" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
@@ -3957,7 +4005,7 @@
         <v>12</v>
       </c>
       <c r="F102" s="3"/>
-      <c r="G102" s="21"/>
+      <c r="G102" s="20"/>
     </row>
     <row r="103" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
@@ -3976,7 +4024,7 @@
         <v>30</v>
       </c>
       <c r="F103" s="3"/>
-      <c r="G103" s="21"/>
+      <c r="G103" s="20"/>
     </row>
     <row r="104" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
@@ -3995,7 +4043,7 @@
         <v>16</v>
       </c>
       <c r="F104" s="5"/>
-      <c r="G104" s="21"/>
+      <c r="G104" s="20"/>
     </row>
     <row r="105" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
@@ -4014,7 +4062,7 @@
         <v>18</v>
       </c>
       <c r="F105" s="3"/>
-      <c r="G105" s="21"/>
+      <c r="G105" s="20"/>
     </row>
     <row r="106" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
@@ -4033,7 +4081,7 @@
         <v>24</v>
       </c>
       <c r="F106" s="4"/>
-      <c r="G106" s="21"/>
+      <c r="G106" s="20"/>
     </row>
     <row r="107" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
@@ -4051,8 +4099,8 @@
       <c r="E107" s="3">
         <v>37</v>
       </c>
-      <c r="F107" s="15"/>
-      <c r="G107" s="13"/>
+      <c r="F107" s="14"/>
+      <c r="G107" s="12"/>
     </row>
     <row r="108" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D108" s="7" t="s">
